--- a/data/raw/landscape-current.xlsx
+++ b/data/raw/landscape-current.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Stakeholders: Community &amp; Civic</t>
+          <t>Stakeholders: Public &amp; Non Profit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">

--- a/data/raw/landscape-current.xlsx
+++ b/data/raw/landscape-current.xlsx
@@ -2133,11 +2133,7 @@
           <t>Group on Reference Quality Data sets (GRQDs)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://www.spglobal.com/</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Focuses on identifying, prioritizing, and preserving “reference-quality” datasets that underpin climate science and key downstream products. The group develops strategies to safeguard high-value, long-term observational records at risk of degradation or loss.</t>
